--- a/presentations/heatmap_byhand/xlsx/baseline_methods/cvss_v3/risk_ranking_filesystemMCP_cvss_v3.xlsx
+++ b/presentations/heatmap_byhand/xlsx/baseline_methods/cvss_v3/risk_ranking_filesystemMCP_cvss_v3.xlsx
@@ -5239,8 +5239,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -5675,12 +5673,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1">
@@ -5699,6 +5698,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="n">
@@ -5714,6 +5718,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AV:N AC:L PR:L UI:N S:C C:H I:H (on .exe/.sys/.bash/.code) → Critical (≥9.0)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="n">
@@ -5729,6 +5738,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AV:N AC:L PR:L UI:N S:C C:H I:H (on executables) → Critical; S:U C:H I:H on others → High</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="n">
@@ -5744,6 +5758,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AV:N AC:L PR:L UI:N S:C I:H A:L (executable move) → High; S:U I:H A:L otherwise → High</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -5759,6 +5778,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AV:N AC:L PR:L UI:N S:U C:H I:N (critical dir + high-sensitivity filetype) → Medium (6.5)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -5774,6 +5798,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AV:N AC:L PR:L UI:N S:U C:L I:N (metadata disclosure on critical/high dirs) → Medium (5.3)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -5789,6 +5818,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AV:N AC:L PR:L UI:N S:U C:L I:N (reveals content existence in sensitive dirs) → Medium (5.3)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -5804,6 +5838,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AV:N AC:L PR:L UI:N S:U C:N I:L (staging path creation) → Medium (4.3)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
@@ -5817,6 +5856,11 @@
       <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AV:N AC:L PR:L UI:N S:U C:L I:N (stat/metadata in critical dirs) → Medium (5.3)</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5881,7 @@
     <col width="5.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="6.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="9.7109375" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="50.5703125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="72" bestFit="1" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6113,11 +6157,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="14.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6136,6 +6181,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="n">
@@ -6151,6 +6201,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Dir tier=critical → C:H I:H read/write; S:C for write_file on executables → Critical worst-case</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="n">
@@ -6166,6 +6221,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Dir tier=critical → C:H I:H; audit-integrity impact elevates to Critical</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="n">
@@ -6181,6 +6241,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Dir tier=high → C:H I:L; write/edit .exe/.code S:C → Critical; read C:H → High</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -6196,6 +6261,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Dir tier=high → C:H I:L; write_file I:H → High worst-case</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -6211,6 +6281,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Dir tier=medium → C:L I:L; write_file I:H → Medium; no executable scope-change uplift</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -6226,6 +6301,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Dir tier=medium → C:L I:L; write_file I:H → Medium worst-case</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
@@ -6241,6 +6321,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Dir tier=medium → C:L I:L; write_file I:H → Medium worst-case</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -6256,7 +6341,13 @@
           <t>Low</t>
         </is>
       </c>
-    </row>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Dir tier=low → C:N/L I:N; list_dir returns N/A; search/read → Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
